--- a/data/trans_orig/P70D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>25958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27293</t>
+          <t>27361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25545</t>
+          <t>25134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>47959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303838</t>
+          <t>305137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>320421</t>
+          <t>320688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229385</t>
+          <t>229317</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245521</t>
+          <t>245616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>539714</t>
+          <t>539814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562228</t>
+          <t>562639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36827</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36088</t>
+          <t>34589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64895</t>
+          <t>65131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>769490</t>
+          <t>770208</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>798149</t>
+          <t>798291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>366072</t>
+          <t>367571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383853</t>
+          <t>383982</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143582</t>
+          <t>1143346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1184898</t>
+          <t>1185334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12877</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27994</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>336638</t>
+          <t>337353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>351424</t>
+          <t>351504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311468</t>
+          <t>311318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321040</t>
+          <t>320762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653719</t>
+          <t>654306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670367</t>
+          <t>670546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39472</t>
+          <t>39310</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>20175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51392</t>
+          <t>52350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>44102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80066</t>
+          <t>82814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>432731</t>
+          <t>432893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454482</t>
+          <t>454857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>429068</t>
+          <t>428110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460261</t>
+          <t>460285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>872597</t>
+          <t>869849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>908550</t>
+          <t>908561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49777</t>
+          <t>50276</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96815</t>
+          <t>101240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67339</t>
+          <t>65658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108218</t>
+          <t>105418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125685</t>
+          <t>124570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196400</t>
+          <t>192169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1870167</t>
+          <t>1865742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1917205</t>
+          <t>1916706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1355425</t>
+          <t>1358225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1396304</t>
+          <t>1397985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3234226</t>
+          <t>3238457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3304941</t>
+          <t>3306056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25958</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17408</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34799</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25134</t>
+          <t>27238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47959</t>
+          <t>50860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>313704</t>
+          <t>345702</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305137</t>
+          <t>334335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>320688</t>
+          <t>352412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>239270</t>
+          <t>258886</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229317</t>
+          <t>248789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245616</t>
+          <t>265310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>552974</t>
+          <t>604587</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>539814</t>
+          <t>591087</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562639</t>
+          <t>614709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>331095</t>
+          <t>364541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>331095</t>
+          <t>364541</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>331095</t>
+          <t>364541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>256678</t>
+          <t>277407</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>256678</t>
+          <t>277407</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>256678</t>
+          <t>277407</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>587773</t>
+          <t>641947</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>587773</t>
+          <t>641947</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>587773</t>
+          <t>641947</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25423</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34589</t>
+          <t>38669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>46759</t>
+          <t>51553</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65131</t>
+          <t>65558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>784981</t>
+          <t>605071</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>770208</t>
+          <t>592161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>798291</t>
+          <t>613602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,22 +1216,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>376737</t>
+          <t>421759</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367571</t>
+          <t>411179</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383982</t>
+          <t>430175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1161718</t>
+          <t>1026831</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143346</t>
+          <t>1012826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1185334</t>
+          <t>1039288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>806317</t>
+          <t>628535</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>806317</t>
+          <t>628535</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>806317</t>
+          <t>628535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>402160</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>402160</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>402160</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1208477</t>
+          <t>1078384</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1208477</t>
+          <t>1078384</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1208477</t>
+          <t>1078384</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>19751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>30818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>345895</t>
+          <t>409979</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>337353</t>
+          <t>401846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>351504</t>
+          <t>416084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>317379</t>
+          <t>329594</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311318</t>
+          <t>323634</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320762</t>
+          <t>334047</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>663274</t>
+          <t>739574</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654306</t>
+          <t>729713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670546</t>
+          <t>746739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>324345</t>
+          <t>338934</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>324345</t>
+          <t>338934</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>324345</t>
+          <t>338934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>681713</t>
+          <t>760531</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>681713</t>
+          <t>760531</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>681713</t>
+          <t>760531</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26704</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39310</t>
+          <t>42201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52350</t>
+          <t>46306</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>60686</t>
+          <t>62889</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44102</t>
+          <t>49334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82814</t>
+          <t>79526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>445499</t>
+          <t>488743</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>432893</t>
+          <t>475660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454857</t>
+          <t>499055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>446477</t>
+          <t>414737</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>428110</t>
+          <t>402201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460285</t>
+          <t>422913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>891977</t>
+          <t>903479</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>869849</t>
+          <t>886842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>908561</t>
+          <t>917034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>480460</t>
+          <t>448507</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>480460</t>
+          <t>448507</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>480460</t>
+          <t>448507</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>952663</t>
+          <t>966368</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>952663</t>
+          <t>966368</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>952663</t>
+          <t>966368</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50276</t>
+          <t>67463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>104557</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65658</t>
+          <t>74678</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105418</t>
+          <t>108319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>172759</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124570</t>
+          <t>149857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>192169</t>
+          <t>202238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1890078</t>
+          <t>1849495</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1865742</t>
+          <t>1827977</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1916706</t>
+          <t>1865071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1379863</t>
+          <t>1424976</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1358225</t>
+          <t>1406377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1397985</t>
+          <t>1440018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3269942</t>
+          <t>3274471</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3238457</t>
+          <t>3244992</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3306056</t>
+          <t>3297373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
